--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R3" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R4" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R3" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R4" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R3" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R4" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R3" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R4" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R3" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R4" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R3" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R4" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R3" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R4" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121258942</v>
+        <v>121258920</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,26 +818,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764459</v>
+        <v>764311</v>
       </c>
       <c r="R3" t="n">
-        <v>7082000</v>
+        <v>7082017</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258920</v>
+        <v>121258942</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764311</v>
+        <v>764459</v>
       </c>
       <c r="R4" t="n">
-        <v>7082017</v>
+        <v>7082000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55683206</v>
+        <v>121258931</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmsjön, Vb</t>
+          <t>Mösjö, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>764460.9835542864</v>
+        <v>764381</v>
       </c>
       <c r="R2" t="n">
-        <v>7082004.004705243</v>
+        <v>7081988</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växte på två gamla granar i närheten av varandra</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +766,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -805,16 +788,11 @@
         <v>121258920</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -912,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121258942</v>
+        <v>55683206</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,27 +918,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mösjö, Vb</t>
+          <t>Holmsjön, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764459</v>
+        <v>764461</v>
       </c>
       <c r="R4" t="n">
-        <v>7082000</v>
+        <v>7082004</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,12 +955,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2015-05-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2015-05-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +979,141 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121258942</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mösjö, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>764459</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7082000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Elin Kannerby</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Elin Kannerby</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49136-2024 artfynd.xlsx
+++ b/artfynd/A 49136-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121258931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121258920</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55683206</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121258942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>